--- a/etf_holdings/2026-09-09_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:31</t>
+          <t>2026-09-09 00:50:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.41%2470</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2470</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:31</t>
+          <t>2026-09-09 00:50:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.82%5340</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-2.82%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5340</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:31</t>
+          <t>2026-09-09 00:50:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.05%4710</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.05%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>4710</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:31</t>
+          <t>2026-09-09 00:50:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.95%3285</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.95%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3285</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:31</t>
+          <t>2026-09-09 00:50:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.53%954</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.53%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>954</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:31</t>
+          <t>2026-09-09 00:50:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.02%2340</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.02%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>2340</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:31</t>
+          <t>2026-09-09 00:50:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+5.56%5795</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+5.56%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>5795</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:31</t>
+          <t>2026-09-09 00:50:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.74%567</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.74%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>567</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:31</t>
+          <t>2026-09-09 00:50:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.86%5550</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.86%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>5550</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:31</t>
+          <t>2026-09-09 00:50:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.43%1805</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.43%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1805</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:31</t>
+          <t>2026-09-09 00:50:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-6.9%1955</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.9%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1955</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:31</t>
+          <t>2026-09-09 00:50:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.2%137</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.2%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>137</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:31</t>
+          <t>2026-09-09 00:50:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.48%618</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.48%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>618</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:31</t>
+          <t>2026-09-09 00:50:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.38%1025</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.38%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>1025</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:31</t>
+          <t>2026-09-09 00:50:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-6.52%1935</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.52%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1935</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:43</t>
+          <t>2026-09-09 00:50:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:43</t>
+          <t>2026-09-09 00:50:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:43</t>
+          <t>2026-09-09 00:50:12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:43</t>
+          <t>2026-09-09 00:50:12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:43</t>
+          <t>2026-09-09 00:50:12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:43</t>
+          <t>2026-09-09 00:50:12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:43</t>
+          <t>2026-09-09 00:50:12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:43</t>
+          <t>2026-09-09 00:50:12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:43</t>
+          <t>2026-09-09 00:50:12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:43</t>
+          <t>2026-09-09 00:50:12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:43</t>
+          <t>2026-09-09 00:50:12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:43</t>
+          <t>2026-09-09 00:50:12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:43</t>
+          <t>2026-09-09 00:50:12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:43</t>
+          <t>2026-09-09 00:50:12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:54</t>
+          <t>2026-09-09 00:50:14</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:54</t>
+          <t>2026-09-09 00:50:14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:54</t>
+          <t>2026-09-09 00:50:14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:54</t>
+          <t>2026-09-09 00:50:14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:54</t>
+          <t>2026-09-09 00:50:14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:54</t>
+          <t>2026-09-09 00:50:14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:54</t>
+          <t>2026-09-09 00:50:14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:54</t>
+          <t>2026-09-09 00:50:14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:54</t>
+          <t>2026-09-09 00:50:14</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:54</t>
+          <t>2026-09-09 00:50:14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:54</t>
+          <t>2026-09-09 00:50:14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:54</t>
+          <t>2026-09-09 00:50:14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:54</t>
+          <t>2026-09-09 00:50:14</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:54</t>
+          <t>2026-09-09 00:50:14</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:36:54</t>
+          <t>2026-09-09 00:50:14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:05</t>
+          <t>2026-09-09 00:50:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:05</t>
+          <t>2026-09-09 00:50:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:05</t>
+          <t>2026-09-09 00:50:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:05</t>
+          <t>2026-09-09 00:50:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:05</t>
+          <t>2026-09-09 00:50:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:05</t>
+          <t>2026-09-09 00:50:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:07</t>
+          <t>2026-09-09 01:15:33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.41%2470</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.41%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2470</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:07</t>
+          <t>2026-09-09 01:15:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.82%5340</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.82%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5340</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:07</t>
+          <t>2026-09-09 01:15:33</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.05%4710</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.05%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4710</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:07</t>
+          <t>2026-09-09 01:15:33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.95%3285</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.95%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3285</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:07</t>
+          <t>2026-09-09 01:15:33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.53%954</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.53%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>954</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:07</t>
+          <t>2026-09-09 01:15:33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-6.02%2340</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-6.02%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2340</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:07</t>
+          <t>2026-09-09 01:15:33</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+5.56%5795</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+5.56%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>5795</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:07</t>
+          <t>2026-09-09 01:15:33</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.74%567</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.74%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>567</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:07</t>
+          <t>2026-09-09 01:15:33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.86%5550</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.86%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5550</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:07</t>
+          <t>2026-09-09 01:15:33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.43%1805</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.43%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1805</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:07</t>
+          <t>2026-09-09 01:15:33</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-6.9%1955</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-6.9%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1955</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:07</t>
+          <t>2026-09-09 01:15:33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.2%137</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.2%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>137</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:07</t>
+          <t>2026-09-09 01:15:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.48%618</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.48%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>618</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:07</t>
+          <t>2026-09-09 01:15:33</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.38%1025</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.38%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1025</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:07</t>
+          <t>2026-09-09 01:15:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-6.52%1935</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-6.52%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1935</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:12</t>
+          <t>2026-09-09 01:15:34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:12</t>
+          <t>2026-09-09 01:15:34</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:12</t>
+          <t>2026-09-09 01:15:34</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:12</t>
+          <t>2026-09-09 01:15:34</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:12</t>
+          <t>2026-09-09 01:15:34</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:12</t>
+          <t>2026-09-09 01:15:34</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:12</t>
+          <t>2026-09-09 01:15:34</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:12</t>
+          <t>2026-09-09 01:15:34</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:12</t>
+          <t>2026-09-09 01:15:34</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:12</t>
+          <t>2026-09-09 01:15:34</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:12</t>
+          <t>2026-09-09 01:15:34</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:12</t>
+          <t>2026-09-09 01:15:34</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:12</t>
+          <t>2026-09-09 01:15:34</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:12</t>
+          <t>2026-09-09 01:15:34</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:14</t>
+          <t>2026-09-09 01:15:35</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:14</t>
+          <t>2026-09-09 01:15:35</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:14</t>
+          <t>2026-09-09 01:15:35</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:14</t>
+          <t>2026-09-09 01:15:35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:14</t>
+          <t>2026-09-09 01:15:35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:14</t>
+          <t>2026-09-09 01:15:35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:14</t>
+          <t>2026-09-09 01:15:35</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:14</t>
+          <t>2026-09-09 01:15:35</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:14</t>
+          <t>2026-09-09 01:15:35</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:14</t>
+          <t>2026-09-09 01:15:35</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:14</t>
+          <t>2026-09-09 01:15:35</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:14</t>
+          <t>2026-09-09 01:15:35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:14</t>
+          <t>2026-09-09 01:15:35</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:14</t>
+          <t>2026-09-09 01:15:35</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:14</t>
+          <t>2026-09-09 01:15:35</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:15</t>
+          <t>2026-09-09 01:15:37</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:15</t>
+          <t>2026-09-09 01:15:37</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:15</t>
+          <t>2026-09-09 01:15:37</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:15</t>
+          <t>2026-09-09 01:15:37</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:15</t>
+          <t>2026-09-09 01:15:37</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:15</t>
+          <t>2026-09-09 01:15:37</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:33</t>
+          <t>2026-09-09 19:32:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.41%2470</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2470</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10.38%11,864,000</t>
+          <t>10.25%11,864,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.38%</t>
+          <t>10.25%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:33</t>
+          <t>2026-09-09 19:32:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +572,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.82%5340</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-2.82%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5340</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.98%4,750,000</t>
+          <t>8.95%4,750,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.98%</t>
+          <t>8.95%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:33</t>
+          <t>2026-09-09 19:32:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +635,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.05%4710</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.05%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>4710</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.65%5,186,000</t>
+          <t>8.41%5,186,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.65%</t>
+          <t>8.41%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:33</t>
+          <t>2026-09-09 19:32:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +693,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.95%3285</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.95%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3285</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.92%5,949,000</t>
+          <t>7.07%20,300,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>7.07%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5949000</v>
+        <v>20300000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:33</t>
+          <t>2026-09-09 19:32:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +756,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.53%954</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.53%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>954</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.86%20,300,000</t>
+          <t>7.05%5,949,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.86%</t>
+          <t>7.05%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>20300000</v>
+        <v>5949000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:33</t>
+          <t>2026-09-09 19:32:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +824,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.02%2340</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.02%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>2340</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.38%6,490,561</t>
+          <t>5.29%6,490,561</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.38%</t>
+          <t>5.29%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:33</t>
+          <t>2026-09-09 19:32:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +887,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+5.56%5795</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+5.56%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>5795</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.23%2,546,000</t>
+          <t>5.01%2,546,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>5.01%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:33</t>
+          <t>2026-09-09 19:32:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +950,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.74%567</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.74%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>567</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.02%24,987,000</t>
+          <t>4.95%24,987,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.02%</t>
+          <t>4.95%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:33</t>
+          <t>2026-09-09 19:32:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +1013,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.86%5550</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.86%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>5550</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.81%2,447,000</t>
+          <t>4.94%2,447,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.81%</t>
+          <t>4.94%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:33</t>
+          <t>2026-09-09 19:32:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1071,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.43%1805</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.43%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1805</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.63%7,240,000</t>
+          <t>4.57%6,464,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.63%</t>
+          <t>4.57%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>7240000</v>
+        <v>6464000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:33</t>
+          <t>2026-09-09 19:32:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1134,40 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-6.9%1955</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.9%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1955</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.48%6,464,000</t>
+          <t>4.55%7,240,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6464000</v>
+        <v>7240000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:33</t>
+          <t>2026-09-09 19:32:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1202,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.2%137</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.2%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>137</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.32%89,118,000</t>
+          <t>4.42%89,118,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.42%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:33</t>
+          <t>2026-09-09 19:32:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1265,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.48%618</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.48%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>618</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.68%16,811,000</t>
+          <t>3.77%16,811,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.77%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:33</t>
+          <t>2026-09-09 19:32:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1328,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.38%1025</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.38%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>1025</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.42%9,426,000</t>
+          <t>3.67%9,426,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:33</t>
+          <t>2026-09-09 19:32:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1391,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-6.52%1935</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.52%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1935</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.93%4,280,848</t>
+          <t>2.96%4,280,848</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:34</t>
+          <t>2026-09-09 19:32:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.82%1345</t>
+          <t>0%1345</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1439,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.57%5,398,000</t>
+          <t>2.54%5,398,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.54%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1452,7 +1482,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:34</t>
+          <t>2026-09-09 19:32:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1482,40 +1512,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+0.03%19220</t>
+          <t>+6.5%2295</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+6.5%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19220</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.42%207,900</t>
+          <t>1.39%1,731,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>207900</v>
+        <v>1731000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:34</t>
+          <t>2026-09-09 19:32:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1545,40 +1575,40 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-4.86%2155</t>
+          <t>-3.2%18605</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-4.86%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>18605</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.32%1,731,000</t>
+          <t>1.36%207,900</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1731000</v>
+        <v>207900</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:34</t>
+          <t>2026-09-09 19:32:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1613,27 +1643,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.65%268.5</t>
+          <t>+0.56%270</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>268.5</t>
+          <t>270</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.22%12,818,450</t>
+          <t>1.21%12,818,450</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1641,7 +1671,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:34</t>
+          <t>2026-09-09 19:32:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1676,27 +1706,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+4.32%3620</t>
+          <t>-0.28%3610</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.82%637,000</t>
+          <t>0.81%637,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1704,7 +1734,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:34</t>
+          <t>2026-09-09 19:32:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1739,27 +1769,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.42%5960</t>
+          <t>-0.59%5925</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.79%372,000</t>
+          <t>0.77%372,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1767,7 +1797,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:34</t>
+          <t>2026-09-09 19:32:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1802,17 +1832,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-3.2%907</t>
+          <t>+0.99%916</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>916</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1830,7 +1860,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:34</t>
+          <t>2026-09-09 19:32:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1865,27 +1895,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.8%505</t>
+          <t>-0.59%502</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>502</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.49%2,712,000</t>
+          <t>0.48%2,712,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1893,7 +1923,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:34</t>
+          <t>2026-09-09 19:32:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1928,27 +1958,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.88%225</t>
+          <t>+3.56%233</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>233</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.40%5,028,000</t>
+          <t>0.41%5,028,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1956,7 +1986,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:34</t>
+          <t>2026-09-09 19:32:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1991,27 +2021,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.21%1225</t>
+          <t>+9.8%1345</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+9.8%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.32%745,000</t>
+          <t>0.35%745,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2019,7 +2049,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:34</t>
+          <t>2026-09-09 19:32:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2054,27 +2084,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+10%7700</t>
+          <t>-5.45%7280</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.26%95,000</t>
+          <t>0.24%95,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2082,7 +2112,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:34</t>
+          <t>2026-09-09 19:32:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2117,17 +2147,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-3.33%188.5</t>
+          <t>+2.65%193.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>188.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2145,7 +2175,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:34</t>
+          <t>2026-09-09 19:32:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2180,17 +2210,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+2.54%605</t>
+          <t>+0.83%610</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+2.54%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>610</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:34</t>
+          <t>2026-09-09 19:32:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2243,17 +2273,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-4.09%223</t>
+          <t>+1.57%226.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-4.09%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>226.5</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2271,7 +2301,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:35</t>
+          <t>2026-09-09 19:32:51</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2306,16 +2336,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-1.45%203.5</t>
+          <t>+1.23%206</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>203.5</v>
+        <v>206</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2332,7 +2362,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:35</t>
+          <t>2026-09-09 19:32:51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2367,16 +2397,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.33%81.7</t>
+          <t>+1.71%83.1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>+1.71%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>81.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2393,7 +2423,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:35</t>
+          <t>2026-09-09 19:32:51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2428,16 +2458,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-4.02%1075</t>
+          <t>+2.33%1100</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-4.02%</t>
+          <t>+2.33%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2454,7 +2484,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:35</t>
+          <t>2026-09-09 19:32:51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2489,16 +2519,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-3.75%231</t>
+          <t>-1.3%228</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:35</t>
+          <t>2026-09-09 19:32:51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2550,16 +2580,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.53%19.1</t>
+          <t>+0.79%19.25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>19.1</v>
+        <v>19.25</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:35</t>
+          <t>2026-09-09 19:32:51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2611,16 +2641,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.97%520</t>
+          <t>+1.15%526</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+1.15%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:35</t>
+          <t>2026-09-09 19:32:51</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2672,16 +2702,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-0.25%4030</t>
+          <t>-3.1%3905</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4030</v>
+        <v>3905</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:35</t>
+          <t>2026-09-09 19:32:51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2733,16 +2763,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.04%76.1</t>
+          <t>-1.58%74.9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.04%</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>76.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:35</t>
+          <t>2026-09-09 19:32:51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2794,16 +2824,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.55%1335</t>
+          <t>-0.37%1330</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:35</t>
+          <t>2026-09-09 19:32:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2855,16 +2885,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-2.4%6500</t>
+          <t>+5.69%6870</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>+5.69%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>6500</v>
+        <v>6870</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:35</t>
+          <t>2026-09-09 19:32:51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2916,16 +2946,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-5.61%328</t>
+          <t>+4.27%342</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-5.61%</t>
+          <t>+4.27%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:35</t>
+          <t>2026-09-09 19:32:51</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2977,16 +3007,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.09%1385</t>
+          <t>-3.97%1330</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1385</v>
+        <v>1330</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:35</t>
+          <t>2026-09-09 19:32:51</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,16 +3068,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+2.71%531</t>
+          <t>-1.51%523</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+2.71%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:35</t>
+          <t>2026-09-09 19:32:51</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3099,16 +3129,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.11%98.1</t>
+          <t>+2.45%100.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>+2.45%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>98.09999999999999</v>
+        <v>100.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:35</t>
+          <t>2026-09-09 19:32:51</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3160,16 +3190,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.57%2265</t>
+          <t>+3.09%2335</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2265</v>
+        <v>2335</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:37</t>
+          <t>2026-09-09 19:32:53</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3221,12 +3251,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.65%955</t>
+          <t>0%955</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:37</t>
+          <t>2026-09-09 19:32:53</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3282,16 +3312,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-3.36%547</t>
+          <t>+0.55%550</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-3.36%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:37</t>
+          <t>2026-09-09 19:32:53</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3343,16 +3373,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-1.1%90.3</t>
+          <t>+1.33%91.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>+1.33%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>90.3</v>
+        <v>91.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:37</t>
+          <t>2026-09-09 19:32:53</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3404,16 +3434,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.76%251.5</t>
+          <t>+0.2%252</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>251.5</v>
+        <v>252</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:37</t>
+          <t>2026-09-09 19:32:53</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3465,16 +3495,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.56%152</t>
+          <t>+3.29%157</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-2.56%</t>
+          <t>+3.29%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:37</t>
+          <t>2026-09-09 19:32:53</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3526,16 +3556,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-3.48%152.5</t>
+          <t>-0.33%152</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-3.48%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>152.5</v>
+        <v>152</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-09_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:46</t>
+          <t>2026-09-09 22:35:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.2%2465</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2465</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:46</t>
+          <t>2026-09-09 22:35:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.66%5375</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.66%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5375</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:46</t>
+          <t>2026-09-09 22:35:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.8%4625</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.8%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4625</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:46</t>
+          <t>2026-09-09 22:35:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+4.09%993</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+4.09%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>993</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:46</t>
+          <t>2026-09-09 22:35:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.89%3380</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.89%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3380</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:46</t>
+          <t>2026-09-09 22:35:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.64%2325</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.64%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2325</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:46</t>
+          <t>2026-09-09 22:35:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.11%5615</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.11%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>5615</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:46</t>
+          <t>2026-09-09 22:35:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.35%565</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>565</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:46</t>
+          <t>2026-09-09 22:35:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+3.78%5760</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+3.78%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5760</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:46</t>
+          <t>2026-09-09 22:35:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+3.07%2015</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+3.07%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2015</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:46</t>
+          <t>2026-09-09 22:35:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.55%1795</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.55%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1795</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:46</t>
+          <t>2026-09-09 22:35:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+3.28%141.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+3.28%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>141.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:46</t>
+          <t>2026-09-09 22:35:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+3.56%640</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+3.56%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>640</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:46</t>
+          <t>2026-09-09 22:35:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+8.29%1110</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+8.29%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1110</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:46</t>
+          <t>2026-09-09 22:35:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.07%1975</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.07%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1975</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:50</t>
+          <t>2026-09-09 22:35:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:50</t>
+          <t>2026-09-09 22:35:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:50</t>
+          <t>2026-09-09 22:35:52</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:50</t>
+          <t>2026-09-09 22:35:52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:50</t>
+          <t>2026-09-09 22:35:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:50</t>
+          <t>2026-09-09 22:35:52</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:50</t>
+          <t>2026-09-09 22:35:52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:50</t>
+          <t>2026-09-09 22:35:52</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:50</t>
+          <t>2026-09-09 22:35:52</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:50</t>
+          <t>2026-09-09 22:35:52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:50</t>
+          <t>2026-09-09 22:35:52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:50</t>
+          <t>2026-09-09 22:35:52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:50</t>
+          <t>2026-09-09 22:35:52</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:50</t>
+          <t>2026-09-09 22:35:52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:51</t>
+          <t>2026-09-09 22:36:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:51</t>
+          <t>2026-09-09 22:36:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:51</t>
+          <t>2026-09-09 22:36:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:51</t>
+          <t>2026-09-09 22:36:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:51</t>
+          <t>2026-09-09 22:36:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:51</t>
+          <t>2026-09-09 22:36:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:51</t>
+          <t>2026-09-09 22:36:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:51</t>
+          <t>2026-09-09 22:36:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:51</t>
+          <t>2026-09-09 22:36:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:51</t>
+          <t>2026-09-09 22:36:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:51</t>
+          <t>2026-09-09 22:36:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:51</t>
+          <t>2026-09-09 22:36:03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:51</t>
+          <t>2026-09-09 22:36:03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:51</t>
+          <t>2026-09-09 22:36:03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:51</t>
+          <t>2026-09-09 22:36:03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:53</t>
+          <t>2026-09-09 22:36:14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:53</t>
+          <t>2026-09-09 22:36:14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:53</t>
+          <t>2026-09-09 22:36:14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:53</t>
+          <t>2026-09-09 22:36:14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:53</t>
+          <t>2026-09-09 22:36:14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:53</t>
+          <t>2026-09-09 22:36:14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:40</t>
+          <t>2026-09-09 22:47:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:40</t>
+          <t>2026-09-09 22:47:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:40</t>
+          <t>2026-09-09 22:47:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:40</t>
+          <t>2026-09-09 22:47:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:40</t>
+          <t>2026-09-09 22:47:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:40</t>
+          <t>2026-09-09 22:47:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:40</t>
+          <t>2026-09-09 22:47:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:40</t>
+          <t>2026-09-09 22:47:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:40</t>
+          <t>2026-09-09 22:47:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:40</t>
+          <t>2026-09-09 22:47:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:40</t>
+          <t>2026-09-09 22:47:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:40</t>
+          <t>2026-09-09 22:47:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:40</t>
+          <t>2026-09-09 22:47:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:40</t>
+          <t>2026-09-09 22:47:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:40</t>
+          <t>2026-09-09 22:47:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:52</t>
+          <t>2026-09-09 22:47:18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:52</t>
+          <t>2026-09-09 22:47:18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:52</t>
+          <t>2026-09-09 22:47:18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:52</t>
+          <t>2026-09-09 22:47:18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:52</t>
+          <t>2026-09-09 22:47:18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:52</t>
+          <t>2026-09-09 22:47:18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:52</t>
+          <t>2026-09-09 22:47:18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:52</t>
+          <t>2026-09-09 22:47:18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:52</t>
+          <t>2026-09-09 22:47:18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:52</t>
+          <t>2026-09-09 22:47:18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:52</t>
+          <t>2026-09-09 22:47:18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:52</t>
+          <t>2026-09-09 22:47:18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:52</t>
+          <t>2026-09-09 22:47:18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:35:52</t>
+          <t>2026-09-09 22:47:18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:03</t>
+          <t>2026-09-09 22:47:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:03</t>
+          <t>2026-09-09 22:47:20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:03</t>
+          <t>2026-09-09 22:47:20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:03</t>
+          <t>2026-09-09 22:47:20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:03</t>
+          <t>2026-09-09 22:47:20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:03</t>
+          <t>2026-09-09 22:47:20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:03</t>
+          <t>2026-09-09 22:47:20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:03</t>
+          <t>2026-09-09 22:47:20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:03</t>
+          <t>2026-09-09 22:47:20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:03</t>
+          <t>2026-09-09 22:47:20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:03</t>
+          <t>2026-09-09 22:47:20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:03</t>
+          <t>2026-09-09 22:47:20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:03</t>
+          <t>2026-09-09 22:47:20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:03</t>
+          <t>2026-09-09 22:47:20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:03</t>
+          <t>2026-09-09 22:47:20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:14</t>
+          <t>2026-09-09 22:47:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:14</t>
+          <t>2026-09-09 22:47:21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:14</t>
+          <t>2026-09-09 22:47:21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:14</t>
+          <t>2026-09-09 22:47:21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:14</t>
+          <t>2026-09-09 22:47:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:14</t>
+          <t>2026-09-09 22:47:21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:15</t>
+          <t>2026-09-09 23:09:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:15</t>
+          <t>2026-09-09 23:09:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:15</t>
+          <t>2026-09-09 23:09:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:15</t>
+          <t>2026-09-09 23:09:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:15</t>
+          <t>2026-09-09 23:09:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:15</t>
+          <t>2026-09-09 23:09:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:15</t>
+          <t>2026-09-09 23:09:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:15</t>
+          <t>2026-09-09 23:09:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:15</t>
+          <t>2026-09-09 23:09:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:15</t>
+          <t>2026-09-09 23:09:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:15</t>
+          <t>2026-09-09 23:09:12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:15</t>
+          <t>2026-09-09 23:09:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:15</t>
+          <t>2026-09-09 23:09:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:15</t>
+          <t>2026-09-09 23:09:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:15</t>
+          <t>2026-09-09 23:09:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:18</t>
+          <t>2026-09-09 23:09:13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:18</t>
+          <t>2026-09-09 23:09:13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:18</t>
+          <t>2026-09-09 23:09:13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:18</t>
+          <t>2026-09-09 23:09:13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:18</t>
+          <t>2026-09-09 23:09:13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:18</t>
+          <t>2026-09-09 23:09:13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:18</t>
+          <t>2026-09-09 23:09:13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:18</t>
+          <t>2026-09-09 23:09:13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:18</t>
+          <t>2026-09-09 23:09:13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:18</t>
+          <t>2026-09-09 23:09:13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:18</t>
+          <t>2026-09-09 23:09:13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:18</t>
+          <t>2026-09-09 23:09:13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:18</t>
+          <t>2026-09-09 23:09:13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:18</t>
+          <t>2026-09-09 23:09:13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:20</t>
+          <t>2026-09-09 23:09:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:20</t>
+          <t>2026-09-09 23:09:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:20</t>
+          <t>2026-09-09 23:09:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:20</t>
+          <t>2026-09-09 23:09:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:20</t>
+          <t>2026-09-09 23:09:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:20</t>
+          <t>2026-09-09 23:09:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:20</t>
+          <t>2026-09-09 23:09:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:20</t>
+          <t>2026-09-09 23:09:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:20</t>
+          <t>2026-09-09 23:09:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:20</t>
+          <t>2026-09-09 23:09:15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:20</t>
+          <t>2026-09-09 23:09:15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:20</t>
+          <t>2026-09-09 23:09:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:20</t>
+          <t>2026-09-09 23:09:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:20</t>
+          <t>2026-09-09 23:09:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:20</t>
+          <t>2026-09-09 23:09:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:21</t>
+          <t>2026-09-09 23:09:16</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:21</t>
+          <t>2026-09-09 23:09:16</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:21</t>
+          <t>2026-09-09 23:09:16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:21</t>
+          <t>2026-09-09 23:09:16</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:21</t>
+          <t>2026-09-09 23:09:16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:21</t>
+          <t>2026-09-09 23:09:16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
